--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10404"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{853F9DDD-A4C3-4E54-A41A-C313DAB2B5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC56F70B-AFA6-5E46-BEB2-423F68BB01E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="31000" windowHeight="16640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,19 +621,26 @@
     </r>
   </si>
   <si>
-    <t>80.6% ( line coverage )</t>
-  </si>
-  <si>
     <t>nu</t>
+  </si>
+  <si>
+    <t>100% ( line coverage )</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -784,13 +791,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1291,43 +1298,43 @@
   </cellStyleXfs>
   <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1335,13 +1342,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1353,19 +1360,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1373,7 +1380,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1381,7 +1388,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1389,218 +1396,218 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2081,26 +2088,26 @@
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:P20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="19.42578125" customWidth="1"/>
+    <col min="15" max="15" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B1" s="8"/>
-      <c r="D1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
-    </row>
-    <row r="2" spans="2:16">
+      <c r="D1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="78"/>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B2" s="31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="15.95">
+    <row r="4" spans="2:16" ht="16" x14ac:dyDescent="0.2">
       <c r="B4" s="39"/>
       <c r="N4" s="5" t="s">
         <v>2</v>
@@ -2108,7 +2115,7 @@
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="2:16" ht="15.95" customHeight="1">
+    <row r="5" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="40"/>
       <c r="C5" s="40"/>
       <c r="D5" s="40"/>
@@ -2125,7 +2132,7 @@
       <c r="O5" s="27"/>
       <c r="P5" s="27"/>
     </row>
-    <row r="6" spans="2:16" ht="15.95" customHeight="1">
+    <row r="6" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
       <c r="D6" s="40"/>
@@ -2144,7 +2151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="15.95" customHeight="1">
+    <row r="7" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
@@ -2165,7 +2172,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="8" spans="2:16">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -2180,7 +2187,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2194,39 +2201,39 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="29"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="2:16" ht="15.95">
+    <row r="12" spans="2:16" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="39" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="224.1" customHeight="1">
-      <c r="B13" s="44" t="s">
+    <row r="13" spans="2:16" ht="224" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
-    </row>
-    <row r="14" spans="2:16" ht="15" customHeight="1">
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+    </row>
+    <row r="14" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
       <c r="D14" s="40"/>
@@ -2238,26 +2245,26 @@
       <c r="J14" s="40"/>
       <c r="K14" s="40"/>
     </row>
-    <row r="15" spans="2:16" ht="38.1" customHeight="1">
-      <c r="B15" s="44" t="s">
+    <row r="15" spans="2:16" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-    </row>
-    <row r="19" spans="2:2">
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
     </row>
   </sheetData>
@@ -2277,374 +2284,366 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:T24"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" customWidth="1"/>
-    <col min="20" max="20" width="47.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.5" customWidth="1"/>
+    <col min="20" max="20" width="47.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20">
+    <row r="1" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B1" s="8"/>
-      <c r="D1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="43"/>
-    </row>
-    <row r="3" spans="2:20">
-      <c r="B3" s="46" t="s">
+      <c r="D1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="78"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B3" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="48"/>
-    </row>
-    <row r="6" spans="2:20">
-      <c r="B6" s="41" t="s">
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="85"/>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B6" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="43"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="78"/>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="Q6" s="41" t="s">
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
+      <c r="Q6" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-    </row>
-    <row r="8" spans="2:20">
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="66"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="I8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="59" t="s">
+      <c r="Q8" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="59"/>
-      <c r="S8" s="59"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="82"/>
       <c r="T8" s="26">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:20">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
       <c r="F9" s="28"/>
       <c r="G9" s="28"/>
       <c r="I9" s="30"/>
-      <c r="Q9" s="59" t="s">
+      <c r="Q9" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="R9" s="59"/>
-      <c r="S9" s="59"/>
+      <c r="R9" s="82"/>
+      <c r="S9" s="82"/>
       <c r="T9" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="2:20">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B10" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
       <c r="F10" s="28"/>
       <c r="G10" s="28"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="52"/>
-      <c r="Q10" s="59" t="s">
+      <c r="I10" s="86"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="87"/>
+      <c r="L10" s="87"/>
+      <c r="M10" s="87"/>
+      <c r="N10" s="87"/>
+      <c r="O10" s="88"/>
+      <c r="Q10" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="R10" s="59" t="s">
+      <c r="R10" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="S10" s="59"/>
+      <c r="S10" s="82"/>
       <c r="T10" s="26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:20">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B11" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
       <c r="F11" s="28"/>
       <c r="G11" s="28"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="55"/>
-    </row>
-    <row r="12" spans="2:20">
+      <c r="I11" s="89"/>
+      <c r="J11" s="90"/>
+      <c r="K11" s="90"/>
+      <c r="L11" s="90"/>
+      <c r="M11" s="90"/>
+      <c r="N11" s="90"/>
+      <c r="O11" s="91"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
       <c r="F12" s="28"/>
       <c r="G12" s="28"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="55"/>
-    </row>
-    <row r="13" spans="2:20">
+      <c r="I12" s="89"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="90"/>
+      <c r="N12" s="90"/>
+      <c r="O12" s="91"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B13" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="55"/>
-      <c r="Q13" s="41" t="s">
+      <c r="I13" s="89"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="90"/>
+      <c r="L13" s="90"/>
+      <c r="M13" s="90"/>
+      <c r="N13" s="90"/>
+      <c r="O13" s="91"/>
+      <c r="Q13" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
-    </row>
-    <row r="14" spans="2:20">
+      <c r="R13" s="66"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="66"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B14" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
       <c r="F14" s="28"/>
       <c r="G14" s="28"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="55"/>
-    </row>
-    <row r="15" spans="2:20">
-      <c r="I15" s="53"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="54"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="55"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="90"/>
+      <c r="O14" s="91"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="I15" s="89"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="90"/>
+      <c r="M15" s="90"/>
+      <c r="N15" s="90"/>
+      <c r="O15" s="91"/>
       <c r="Q15" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="R15" s="60" t="s">
+      <c r="R15" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="S15" s="60"/>
-      <c r="T15" s="60"/>
-    </row>
-    <row r="16" spans="2:20">
-      <c r="I16" s="53"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="55"/>
+      <c r="S15" s="95"/>
+      <c r="T15" s="95"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="I16" s="89"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="90"/>
+      <c r="O16" s="91"/>
       <c r="Q16" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="R16" s="45" t="s">
+      <c r="R16" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
-    </row>
-    <row r="17" spans="9:20">
-      <c r="I17" s="53"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="55"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
+    </row>
+    <row r="17" spans="9:20" x14ac:dyDescent="0.2">
+      <c r="I17" s="89"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="90"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="91"/>
       <c r="Q17" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R17" s="45" t="s">
+      <c r="R17" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
-    </row>
-    <row r="18" spans="9:20">
-      <c r="I18" s="53"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="55"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="80"/>
+    </row>
+    <row r="18" spans="9:20" x14ac:dyDescent="0.2">
+      <c r="I18" s="89"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="91"/>
       <c r="Q18" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="R18" s="45" t="s">
+      <c r="R18" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-    </row>
-    <row r="19" spans="9:20">
-      <c r="I19" s="53"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="55"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+    </row>
+    <row r="19" spans="9:20" x14ac:dyDescent="0.2">
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="90"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="91"/>
       <c r="Q19" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="R19" s="45" t="s">
+      <c r="R19" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="S19" s="45"/>
-      <c r="T19" s="45"/>
-    </row>
-    <row r="20" spans="9:20">
-      <c r="I20" s="53"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="55"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+    </row>
+    <row r="20" spans="9:20" x14ac:dyDescent="0.2">
+      <c r="I20" s="89"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="91"/>
       <c r="Q20" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="R20" s="45" t="s">
+      <c r="R20" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="S20" s="45"/>
-      <c r="T20" s="45"/>
-    </row>
-    <row r="21" spans="9:20">
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="55"/>
+      <c r="S20" s="80"/>
+      <c r="T20" s="80"/>
+    </row>
+    <row r="21" spans="9:20" x14ac:dyDescent="0.2">
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="90"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="90"/>
+      <c r="O21" s="91"/>
       <c r="Q21" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="R21" s="45" t="s">
+      <c r="R21" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-    </row>
-    <row r="22" spans="9:20">
-      <c r="I22" s="53"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="55"/>
-    </row>
-    <row r="23" spans="9:20">
-      <c r="I23" s="53"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="55"/>
-    </row>
-    <row r="24" spans="9:20">
-      <c r="I24" s="56"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="57"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="58"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+    </row>
+    <row r="22" spans="9:20" x14ac:dyDescent="0.2">
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="90"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="91"/>
+    </row>
+    <row r="23" spans="9:20" x14ac:dyDescent="0.2">
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="91"/>
+    </row>
+    <row r="24" spans="9:20" x14ac:dyDescent="0.2">
+      <c r="I24" s="92"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="93"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R20:T20"/>
     <mergeCell ref="R21:T21"/>
@@ -2661,6 +2660,14 @@
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="R17:T17"/>
     <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2674,212 +2681,212 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:AE17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" customWidth="1"/>
+    <col min="11" max="11" width="9.5" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="15" width="13.42578125" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
-    <col min="19" max="19" width="11.85546875" customWidth="1"/>
-    <col min="20" max="21" width="8.85546875" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" customWidth="1"/>
-    <col min="26" max="26" width="3.85546875" customWidth="1"/>
-    <col min="27" max="28" width="3.140625" customWidth="1"/>
+    <col min="13" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="10.5" customWidth="1"/>
+    <col min="17" max="17" width="12.1640625" customWidth="1"/>
+    <col min="19" max="19" width="11.83203125" customWidth="1"/>
+    <col min="20" max="21" width="8.83203125" customWidth="1"/>
+    <col min="25" max="25" width="9.1640625" customWidth="1"/>
+    <col min="26" max="26" width="3.83203125" customWidth="1"/>
+    <col min="27" max="28" width="3.1640625" customWidth="1"/>
     <col min="29" max="29" width="4" customWidth="1"/>
-    <col min="30" max="30" width="3.85546875" customWidth="1"/>
-    <col min="31" max="31" width="5.42578125" customWidth="1"/>
+    <col min="30" max="30" width="3.83203125" customWidth="1"/>
+    <col min="31" max="31" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31">
+    <row r="1" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B1" s="8"/>
-      <c r="D1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
-    </row>
-    <row r="3" spans="2:31">
-      <c r="B3" s="61" t="s">
+      <c r="D1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="78"/>
+    </row>
+    <row r="3" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B3" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="48"/>
-    </row>
-    <row r="5" spans="2:31">
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="85"/>
+    </row>
+    <row r="5" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B5" s="7"/>
     </row>
-    <row r="6" spans="2:31" ht="15.95">
-      <c r="B6" s="62" t="s">
+    <row r="6" spans="2:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="107" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="62"/>
-      <c r="AB6" s="62"/>
-      <c r="AC6" s="62"/>
-      <c r="AD6" s="62"/>
-      <c r="AE6" s="62"/>
-    </row>
-    <row r="7" spans="2:31" ht="15.95">
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="74" t="s">
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="107"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="107"/>
+      <c r="S6" s="107"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="107"/>
+      <c r="W6" s="107"/>
+      <c r="X6" s="107"/>
+      <c r="Y6" s="107"/>
+      <c r="Z6" s="107"/>
+      <c r="AA6" s="107"/>
+      <c r="AB6" s="107"/>
+      <c r="AC6" s="107"/>
+      <c r="AD6" s="107"/>
+      <c r="AE6" s="107"/>
+    </row>
+    <row r="7" spans="2:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="69" t="s">
+      <c r="F7" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="69"/>
-      <c r="P7" s="69"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="69"/>
-      <c r="T7" s="66" t="s">
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="99"/>
+      <c r="T7" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="U7" s="66"/>
-      <c r="V7" s="66"/>
-      <c r="W7" s="66"/>
-      <c r="X7" s="66"/>
-      <c r="Y7" s="66"/>
-      <c r="Z7" s="65" t="s">
+      <c r="U7" s="100"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="100"/>
+      <c r="X7" s="100"/>
+      <c r="Y7" s="100"/>
+      <c r="Z7" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="AA7" s="65"/>
-      <c r="AB7" s="65"/>
-      <c r="AC7" s="65"/>
-      <c r="AD7" s="65"/>
-      <c r="AE7" s="65"/>
-    </row>
-    <row r="8" spans="2:31" ht="33" customHeight="1">
-      <c r="B8" s="62"/>
-      <c r="C8" s="67" t="s">
+      <c r="AA7" s="101"/>
+      <c r="AB7" s="101"/>
+      <c r="AC7" s="101"/>
+      <c r="AD7" s="101"/>
+      <c r="AE7" s="101"/>
+    </row>
+    <row r="8" spans="2:31" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="107"/>
+      <c r="C8" s="96" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="74"/>
-      <c r="F8" s="69" t="s">
+      <c r="E8" s="98"/>
+      <c r="F8" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69" t="s">
+      <c r="G8" s="99"/>
+      <c r="H8" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69" t="s">
+      <c r="I8" s="99"/>
+      <c r="J8" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69" t="s">
+      <c r="K8" s="99"/>
+      <c r="L8" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="M8" s="69"/>
-      <c r="N8" s="72" t="s">
+      <c r="M8" s="99"/>
+      <c r="N8" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="O8" s="73"/>
-      <c r="P8" s="72" t="s">
+      <c r="O8" s="105"/>
+      <c r="P8" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="Q8" s="73"/>
-      <c r="R8" s="72" t="s">
+      <c r="Q8" s="105"/>
+      <c r="R8" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="S8" s="73"/>
-      <c r="T8" s="70" t="s">
+      <c r="S8" s="105"/>
+      <c r="T8" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="U8" s="70" t="s">
+      <c r="U8" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="V8" s="70" t="s">
+      <c r="V8" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="W8" s="70" t="s">
+      <c r="W8" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="X8" s="70" t="s">
+      <c r="X8" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="Y8" s="66" t="s">
+      <c r="Y8" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="Z8" s="65">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="65">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="65">
+      <c r="Z8" s="101">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="101">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="101">
         <v>2</v>
       </c>
-      <c r="AC8" s="65" t="s">
+      <c r="AC8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="AD8" s="65" t="s">
+      <c r="AD8" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="AE8" s="65" t="s">
+      <c r="AE8" s="101" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="2:31" ht="17.100000000000001">
-      <c r="B9" s="62"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="74"/>
+    <row r="9" spans="2:31" ht="17" x14ac:dyDescent="0.2">
+      <c r="B9" s="107"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="98"/>
       <c r="F9" s="9" t="s">
         <v>70</v>
       </c>
@@ -2922,20 +2929,20 @@
       <c r="S9" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="T9" s="71"/>
-      <c r="U9" s="71"/>
-      <c r="V9" s="71"/>
-      <c r="W9" s="71"/>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="66"/>
-      <c r="Z9" s="65"/>
-      <c r="AA9" s="65"/>
-      <c r="AB9" s="65"/>
-      <c r="AC9" s="65"/>
-      <c r="AD9" s="65"/>
-      <c r="AE9" s="65"/>
-    </row>
-    <row r="10" spans="2:31" ht="33.950000000000003">
+      <c r="T9" s="103"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103"/>
+      <c r="Y9" s="100"/>
+      <c r="Z9" s="101"/>
+      <c r="AA9" s="101"/>
+      <c r="AB9" s="101"/>
+      <c r="AC9" s="101"/>
+      <c r="AD9" s="101"/>
+      <c r="AE9" s="101"/>
+    </row>
+    <row r="10" spans="2:31" ht="34" x14ac:dyDescent="0.2">
       <c r="B10" s="10" t="s">
         <v>72</v>
       </c>
@@ -3027,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:31" ht="48.95" customHeight="1">
+    <row r="11" spans="2:31" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="10" t="s">
         <v>76</v>
       </c>
@@ -3119,7 +3126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:31" ht="33.950000000000003">
+    <row r="12" spans="2:31" ht="34" x14ac:dyDescent="0.2">
       <c r="B12" s="10" t="s">
         <v>80</v>
       </c>
@@ -3211,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:31" ht="54.95" customHeight="1">
+    <row r="13" spans="2:31" ht="55" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="10" t="s">
         <v>82</v>
       </c>
@@ -3303,7 +3310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:31" ht="56.1" customHeight="1">
+    <row r="14" spans="2:31" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="10" t="s">
         <v>86</v>
       </c>
@@ -3395,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:31" ht="62.1" customHeight="1">
+    <row r="15" spans="2:31" ht="62" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="10" t="s">
         <v>90</v>
       </c>
@@ -3487,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:31" ht="68.099999999999994">
+    <row r="16" spans="2:31" ht="68" x14ac:dyDescent="0.2">
       <c r="B16" s="10" t="s">
         <v>94</v>
       </c>
@@ -3579,7 +3586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:31" ht="68.099999999999994">
+    <row r="17" spans="2:31" ht="68" x14ac:dyDescent="0.2">
       <c r="B17" s="10" t="s">
         <v>96</v>
       </c>
@@ -3673,21 +3680,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:S7"/>
-    <mergeCell ref="T7:Y7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
@@ -3704,6 +3696,21 @@
     <mergeCell ref="X8:X9"/>
     <mergeCell ref="Z7:AE7"/>
     <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:S7"/>
+    <mergeCell ref="T7:Y7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3717,60 +3724,60 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:J19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.85546875" customWidth="1"/>
-    <col min="6" max="6" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" customWidth="1"/>
     <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="34.42578125" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="34.5" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B1" s="8"/>
-      <c r="D1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-    </row>
-    <row r="3" spans="2:10">
-      <c r="B3" s="77" t="s">
+      <c r="D1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-    </row>
-    <row r="4" spans="2:10">
-      <c r="B4" s="78" t="s">
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B4" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="87" t="s">
+      <c r="D4" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="80" t="s">
+      <c r="E4" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="84"/>
-      <c r="G4" s="80" t="s">
+      <c r="F4" s="74"/>
+      <c r="G4" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="H4" s="81"/>
-    </row>
-    <row r="5" spans="2:10" ht="15.95" thickBot="1">
-      <c r="B5" s="79"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="88"/>
+      <c r="H4" s="71"/>
+    </row>
+    <row r="5" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="69"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="77"/>
       <c r="E5" s="2" t="s">
         <v>104</v>
       </c>
@@ -3784,11 +3791,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="32.25">
+    <row r="6" spans="2:10" ht="17" x14ac:dyDescent="0.2">
       <c r="B6" s="13">
         <v>16</v>
       </c>
-      <c r="C6" s="82" t="s">
+      <c r="C6" s="72" t="s">
         <v>108</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -3803,15 +3810,15 @@
       <c r="G6" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="105" t="s">
+      <c r="H6" s="41" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="32.25">
+    <row r="7" spans="2:10" ht="34" x14ac:dyDescent="0.2">
       <c r="B7" s="13">
         <v>17</v>
       </c>
-      <c r="C7" s="82"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="4" t="s">
         <v>111</v>
       </c>
@@ -3824,15 +3831,15 @@
       <c r="G7" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="106" t="s">
+      <c r="H7" s="42" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="32.25">
+    <row r="8" spans="2:10" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="13">
         <v>18</v>
       </c>
-      <c r="C8" s="82"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="4" t="s">
         <v>113</v>
       </c>
@@ -3845,15 +3852,15 @@
       <c r="G8" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="106" t="s">
+      <c r="H8" s="42" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="60.75">
+    <row r="9" spans="2:10" ht="48" x14ac:dyDescent="0.2">
       <c r="B9" s="13">
         <v>19</v>
       </c>
-      <c r="C9" s="82"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="4" t="s">
         <v>115</v>
       </c>
@@ -3866,15 +3873,15 @@
       <c r="G9" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="107" t="s">
+      <c r="H9" s="43" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="60.75">
+    <row r="10" spans="2:10" ht="48" x14ac:dyDescent="0.2">
       <c r="B10" s="13">
         <v>20</v>
       </c>
-      <c r="C10" s="82"/>
+      <c r="C10" s="72"/>
       <c r="D10" s="4" t="s">
         <v>117</v>
       </c>
@@ -3887,15 +3894,15 @@
       <c r="G10" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="H10" s="106" t="s">
+      <c r="H10" s="42" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="60.75">
+    <row r="11" spans="2:10" ht="48" x14ac:dyDescent="0.2">
       <c r="B11" s="13">
         <v>21</v>
       </c>
-      <c r="C11" s="82"/>
+      <c r="C11" s="72"/>
       <c r="D11" s="4" t="s">
         <v>119</v>
       </c>
@@ -3908,15 +3915,15 @@
       <c r="G11" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="H11" s="108" t="s">
+      <c r="H11" s="44" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="76.5">
+    <row r="12" spans="2:10" ht="64" x14ac:dyDescent="0.2">
       <c r="B12" s="13">
         <v>22</v>
       </c>
-      <c r="C12" s="82"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="4" t="s">
         <v>121</v>
       </c>
@@ -3929,15 +3936,15 @@
       <c r="G12" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="108" t="s">
+      <c r="H12" s="44" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="76.5">
+    <row r="13" spans="2:10" ht="64" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>23</v>
       </c>
-      <c r="C13" s="83"/>
+      <c r="C13" s="73"/>
       <c r="D13" s="4" t="s">
         <v>123</v>
       </c>
@@ -3950,11 +3957,11 @@
       <c r="G13" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="109" t="s">
+      <c r="H13" s="45" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="15.95" thickTop="1">
+    <row r="14" spans="2:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -3963,70 +3970,70 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="2:10" ht="15.95" thickBot="1">
+    <row r="15" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>125</v>
       </c>
       <c r="G15" s="15"/>
     </row>
-    <row r="16" spans="2:10" ht="17.100000000000001" thickTop="1" thickBot="1">
-      <c r="B16" s="75" t="s">
+    <row r="16" spans="2:10" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
       <c r="F16" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="76"/>
-      <c r="H16" s="92"/>
-      <c r="I16" s="97" t="s">
+      <c r="G16" s="57"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="J16" s="98"/>
-    </row>
-    <row r="17" spans="2:10" ht="15.95" thickTop="1">
-      <c r="B17" s="96" t="s">
+      <c r="J16" s="63"/>
+    </row>
+    <row r="17" spans="2:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="100" t="s">
+      <c r="C17" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="100" t="s">
+      <c r="D17" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="E17" s="102" t="s">
+      <c r="E17" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="89" t="s">
+      <c r="F17" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="G17" s="90" t="s">
+      <c r="G17" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="I17" s="95" t="s">
+      <c r="I17" s="61" t="s">
         <v>136</v>
       </c>
-      <c r="J17" s="85" t="s">
+      <c r="J17" s="54" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="99"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="89"/>
-    </row>
-    <row r="19" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" s="47"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="52"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="19">
         <f>SUM(C19:D19)</f>
         <v>8</v>
@@ -4038,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F19" s="18">
         <v>0</v>
@@ -4048,7 +4055,7 @@
       </c>
       <c r="H19" s="21"/>
       <c r="I19" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J19" s="22">
         <f>C19</f>
@@ -4057,17 +4064,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I16:J16"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="B3:H3"/>
@@ -4077,8 +4073,19 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4091,15 +4098,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4237,14 +4235,46 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A94B7F00-F329-4E8F-A3EE-411E39CDE676}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A94B7F00-F329-4E8F-A3EE-411E39CDE676}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>